--- a/src/benchmark/GraphBLAS v10 vs GAP benchmarks.xlsx
+++ b/src/benchmark/GraphBLAS v10 vs GAP benchmarks.xlsx
@@ -959,7 +959,7 @@
         <f t="shared" ref="H35:H41" si="3">median(B35:F35)</f>
         <v>0.6044164038</v>
       </c>
-      <c r="I35" s="9">
+      <c r="I35" s="3">
         <f t="shared" ref="I35:I41" si="4">1/H35</f>
         <v>1.654488518</v>
       </c>
@@ -1029,7 +1029,7 @@
         <f t="shared" si="3"/>
         <v>0.5239870257</v>
       </c>
-      <c r="I37" s="9">
+      <c r="I37" s="3">
         <f t="shared" si="4"/>
         <v>1.9084442</v>
       </c>
@@ -1064,7 +1064,7 @@
         <f t="shared" si="3"/>
         <v>0.1987125288</v>
       </c>
-      <c r="I38" s="9">
+      <c r="I38" s="3">
         <f t="shared" si="4"/>
         <v>5.03239532</v>
       </c>
@@ -1099,7 +1099,7 @@
         <f t="shared" si="3"/>
         <v>0.3345104751</v>
       </c>
-      <c r="I39" s="9">
+      <c r="I39" s="3">
         <f t="shared" si="4"/>
         <v>2.989443005</v>
       </c>
@@ -1134,7 +1134,7 @@
         <f t="shared" si="3"/>
         <v>0.6986427781</v>
       </c>
-      <c r="I40" s="9">
+      <c r="I40" s="3">
         <f t="shared" si="4"/>
         <v>1.43134665</v>
       </c>
